--- a/D_Documentation/Alex/Bauteile2.xlsx
+++ b/D_Documentation/Alex/Bauteile2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\Diplomarbeit\Git\3D_Scanner_New\3D_Scanner\D_Documentation\Alex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{170EE238-786B-4009-9E73-38B4786999DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6456231C-7C56-4615-A605-7704ADF6957D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F4CA4B4-969C-4233-90C4-7AF8CE384A73}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8F4CA4B4-969C-4233-90C4-7AF8CE384A73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,25 +36,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>https://at.rs-online.com/web/p/usb-kabel/1828869</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/Tripp-Lite/UR050-06N?qs=iC14BvcgY%2F1zyNw5IF8Oiw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://eu.mouser.com/ProductDetail/CUI-Inc/SUA-A-B?qs=olJun0bQHM8hk1uKNM%2FseQ%3D%3D</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+  <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Mouser</t>
+  </si>
+  <si>
+    <t>Liferantennummer</t>
+  </si>
+  <si>
+    <t>545-UR050-06N</t>
+  </si>
+  <si>
+    <t>Micro-USB Kabel</t>
+  </si>
+  <si>
+    <t>Lieferant</t>
+  </si>
+  <si>
+    <t>USB-C Adapter</t>
+  </si>
+  <si>
+    <t>aktiver USB-Hub</t>
+  </si>
+  <si>
+    <t>490-SUA-A-B</t>
+  </si>
+  <si>
+    <t>545-U360-004-2F</t>
+  </si>
+  <si>
+    <t>Einzelpreis [€]</t>
+  </si>
+  <si>
+    <t>Anzahl</t>
+  </si>
+  <si>
+    <t>Gesamtpreis [€]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="#,##0.00\ [$€-1];[Red]\-#,##0.00\ [$€-1]"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -77,13 +129,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -416,28 +482,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08AF118-9016-4362-9853-D49C9A137C61}">
-  <dimension ref="C5:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="97.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C5" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>1</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>5.03</v>
+      </c>
+      <c r="G3" s="4">
+        <v>5.03</v>
       </c>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.17</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4">
+        <v>51.46</v>
+      </c>
+      <c r="G5" s="4">
+        <v>51.46</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{565CD808-5264-447D-AFDE-68C70961EB14}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{451226EA-6ED6-490A-8E06-AFA88EE2649C}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{A2C5CA3A-3B13-465B-B3BC-835D84513C54}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>